--- a/docs/grille-audit-easy-checks.xlsx
+++ b/docs/grille-audit-easy-checks.xlsx
@@ -4192,7 +4192,7 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>À 200 % et dans une fenêtre étroite, les contenus restent-ils lisibles et utilisables sans perte d'information ?</t>
+          <t>À 200 %, dans une fenêtre étroite et avec un espacement du texte renforcé, les contenus restent-ils lisibles et utilisables sans perte d'information ?</t>
         </is>
       </c>
     </row>
@@ -4204,7 +4204,7 @@
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>1.4.4 - Redimensionnement du texte ; 1.4.10 - Redistribution</t>
+          <t>1.4.4 - Redimensionnement du texte ; 1.4.10 - Redistribution ; 1.4.12 - Espacement du texte</t>
         </is>
       </c>
     </row>
@@ -4216,7 +4216,7 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>10.4, 10.11</t>
+          <t>10.4, 10.11, 10.12</t>
         </is>
       </c>
     </row>
@@ -4228,7 +4228,7 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Zoomer à 200 %, puis tester séparément une zone d'affichage de 320 CSS px et parcourir tout le contenu.</t>
+          <t>Zoomer à 200 %, puis tester séparément une zone d'affichage de 320 CSS px. Activer ensuite le bookmarklet « 10.12 Espacement » et parcourir tout le contenu.</t>
         </is>
       </c>
     </row>
@@ -4240,7 +4240,7 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>Aucun texte coupé ou superposé. Contenus et commandes utilisables. Pas de défilement dans deux directions pour lire le contenu courant.</t>
+          <t>Aucun texte coupé ou superposé. Contenus et commandes utilisables. Pas de défilement dans deux directions pour lire le contenu courant. Aucun contenu perdu après modification de l'espacement du texte.</t>
         </is>
       </c>
     </row>

--- a/docs/grille-audit-easy-checks.xlsx
+++ b/docs/grille-audit-easy-checks.xlsx
@@ -2124,7 +2124,7 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Cliquer sur chaque libellé, vérifier le nom accessible et contrôler les légendes des groupes.</t>
+          <t>Repérer les champs et leurs étiquettes avec le bookmarklet « 11.1 Formulaires », Tanaguru ou WAVE. Cliquer sur chaque libellé, vérifier le nom accessible et contrôler les légendes des groupes.</t>
         </is>
       </c>
     </row>
